--- a/data.xlsx
+++ b/data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="1192">
   <si>
     <t>nm</t>
   </si>
@@ -2653,13 +2653,10 @@
     <t>河北省唐山市路北区河北路办事处河西路河北三号</t>
   </si>
   <si>
-    <t xml:space="preserve">电表 </t>
+    <t>电表</t>
   </si>
   <si>
     <t>河北省唐山市高新技术开发区高新区街道办事处火炬路世纪龙庭</t>
-  </si>
-  <si>
-    <t>电表</t>
   </si>
   <si>
     <t>河北省唐山市路北区钓鱼台办事处朝阳道张各庄楼</t>
@@ -25315,7 +25312,7 @@
         <v>13</v>
       </c>
       <c r="I843" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J843" s="8">
         <v>10800</v>
@@ -25327,7 +25324,7 @@
         <v>18</v>
       </c>
       <c r="B844" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C844" s="4">
         <v>237</v>
@@ -25344,7 +25341,7 @@
         <v>13</v>
       </c>
       <c r="I844" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J844" s="8">
         <v>3159.68</v>
@@ -25356,7 +25353,7 @@
         <v>33</v>
       </c>
       <c r="B845" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C845" s="4">
         <v>816</v>
@@ -25375,7 +25372,7 @@
         <v>408</v>
       </c>
       <c r="I845" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J845" s="8">
         <v>14089</v>
@@ -25387,7 +25384,7 @@
         <v>20</v>
       </c>
       <c r="B846" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C846" s="4">
         <v>432</v>
@@ -25406,7 +25403,7 @@
         <v>70</v>
       </c>
       <c r="I846" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J846" s="8">
         <v>12036</v>
@@ -25418,7 +25415,7 @@
         <v>33</v>
       </c>
       <c r="B847" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C847" s="4">
         <v>297</v>
@@ -25435,7 +25432,7 @@
         <v>13</v>
       </c>
       <c r="I847" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J847" s="8">
         <v>4142</v>
@@ -25447,7 +25444,7 @@
         <v>18</v>
       </c>
       <c r="B848" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C848" s="4">
         <v>255</v>
@@ -25464,7 +25461,7 @@
         <v>13</v>
       </c>
       <c r="I848" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J848" s="8">
         <v>196.88</v>
@@ -25476,7 +25473,7 @@
         <v>33</v>
       </c>
       <c r="B849" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C849" s="4">
         <v>163</v>
@@ -25493,7 +25490,7 @@
         <v>13</v>
       </c>
       <c r="I849" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J849" s="8">
         <v>11472</v>
@@ -25505,7 +25502,7 @@
         <v>24</v>
       </c>
       <c r="B850" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C850" s="4">
         <v>76</v>
@@ -25522,7 +25519,7 @@
         <v>13</v>
       </c>
       <c r="I850" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J850" s="8">
         <v>2751.6</v>
@@ -25534,7 +25531,7 @@
         <v>24</v>
       </c>
       <c r="B851" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C851" s="4">
         <v>403</v>
@@ -25551,7 +25548,7 @@
         <v>13</v>
       </c>
       <c r="I851" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J851" s="8"/>
       <c r="K851" s="4"/>
@@ -25561,7 +25558,7 @@
         <v>24</v>
       </c>
       <c r="B852" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C852" s="4">
         <v>377</v>
@@ -25578,7 +25575,7 @@
         <v>13</v>
       </c>
       <c r="I852" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J852" s="8"/>
       <c r="K852" s="4"/>
@@ -25588,7 +25585,7 @@
         <v>24</v>
       </c>
       <c r="B853" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C853" s="4">
         <v>246</v>
@@ -25605,7 +25602,7 @@
         <v>13</v>
       </c>
       <c r="I853" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J853" s="8"/>
       <c r="K853" s="4"/>
@@ -25615,7 +25612,7 @@
         <v>24</v>
       </c>
       <c r="B854" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C854" s="4">
         <v>54</v>
@@ -25634,7 +25631,7 @@
         <v>70</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J854" s="8"/>
       <c r="K854" s="4"/>
@@ -25644,7 +25641,7 @@
         <v>24</v>
       </c>
       <c r="B855" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C855" s="4">
         <v>687</v>
@@ -25661,7 +25658,7 @@
         <v>13</v>
       </c>
       <c r="I855" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J855" s="8">
         <v>10026</v>
@@ -25673,7 +25670,7 @@
         <v>20</v>
       </c>
       <c r="B856" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C856" s="4">
         <v>110</v>
@@ -25690,13 +25687,13 @@
         <v>13</v>
       </c>
       <c r="I856" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J856" s="8">
         <v>7012</v>
       </c>
       <c r="K856" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="857" customHeight="1" spans="1:11">
@@ -25704,7 +25701,7 @@
         <v>20</v>
       </c>
       <c r="B857" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C857" s="4">
         <v>89</v>
@@ -25721,7 +25718,7 @@
         <v>13</v>
       </c>
       <c r="I857" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J857" s="8">
         <v>2586</v>
@@ -25733,7 +25730,7 @@
         <v>24</v>
       </c>
       <c r="B858" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C858" s="4">
         <v>35</v>
@@ -25750,7 +25747,7 @@
         <v>13</v>
       </c>
       <c r="I858" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J858" s="8">
         <v>1800</v>
@@ -25762,7 +25759,7 @@
         <v>24</v>
       </c>
       <c r="B859" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C859" s="4">
         <v>211</v>
@@ -25779,7 +25776,7 @@
         <v>13</v>
       </c>
       <c r="I859" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J859" s="8"/>
       <c r="K859" s="4"/>
@@ -25789,7 +25786,7 @@
         <v>11</v>
       </c>
       <c r="B860" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C860" s="4">
         <v>32</v>
@@ -25806,13 +25803,13 @@
         <v>13</v>
       </c>
       <c r="I860" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J860" s="8">
         <v>2600</v>
       </c>
       <c r="K860" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="861" customHeight="1" spans="1:11">
@@ -25820,7 +25817,7 @@
         <v>11</v>
       </c>
       <c r="B861" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C861" s="4">
         <v>25</v>
@@ -25837,13 +25834,13 @@
         <v>13</v>
       </c>
       <c r="I861" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J861" s="8">
         <v>5580</v>
       </c>
       <c r="K861" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="862" customHeight="1" spans="1:11">
@@ -25851,7 +25848,7 @@
         <v>20</v>
       </c>
       <c r="B862" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C862" s="4">
         <v>56</v>
@@ -25868,13 +25865,13 @@
         <v>13</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J862" s="8">
         <v>780</v>
       </c>
       <c r="K862" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="863" customHeight="1" spans="1:11">
@@ -25882,7 +25879,7 @@
         <v>24</v>
       </c>
       <c r="B863" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C863" s="4">
         <v>5</v>
@@ -25901,7 +25898,7 @@
         <v>436</v>
       </c>
       <c r="I863" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J863" s="8"/>
       <c r="K863" s="4"/>
@@ -25911,7 +25908,7 @@
         <v>24</v>
       </c>
       <c r="B864" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C864" s="4">
         <v>318</v>
@@ -25928,7 +25925,7 @@
         <v>13</v>
       </c>
       <c r="I864" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J864" s="8"/>
       <c r="K864" s="4"/>
@@ -25938,7 +25935,7 @@
         <v>24</v>
       </c>
       <c r="B865" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C865" s="4">
         <v>270</v>
@@ -25955,7 +25952,7 @@
         <v>13</v>
       </c>
       <c r="I865" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J865" s="8"/>
       <c r="K865" s="4"/>
@@ -25965,7 +25962,7 @@
         <v>33</v>
       </c>
       <c r="B866" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C866" s="4">
         <v>264</v>
@@ -25982,7 +25979,7 @@
         <v>13</v>
       </c>
       <c r="I866" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J866" s="8"/>
       <c r="K866" s="4"/>
@@ -25992,7 +25989,7 @@
         <v>33</v>
       </c>
       <c r="B867" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C867" s="4">
         <v>230</v>
@@ -26009,7 +26006,7 @@
         <v>13</v>
       </c>
       <c r="I867" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J867" s="8"/>
       <c r="K867" s="4"/>
@@ -26019,7 +26016,7 @@
         <v>24</v>
       </c>
       <c r="B868" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C868" s="4">
         <v>220</v>
@@ -26036,7 +26033,7 @@
         <v>13</v>
       </c>
       <c r="I868" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J868" s="8"/>
       <c r="K868" s="4"/>
@@ -26046,7 +26043,7 @@
         <v>24</v>
       </c>
       <c r="B869" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C869" s="4">
         <v>83</v>
@@ -26063,7 +26060,7 @@
         <v>13</v>
       </c>
       <c r="I869" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J869" s="8"/>
       <c r="K869" s="4"/>
@@ -26073,7 +26070,7 @@
         <v>33</v>
       </c>
       <c r="B870" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C870" s="4">
         <v>66</v>
@@ -26090,7 +26087,7 @@
         <v>13</v>
       </c>
       <c r="I870" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J870" s="8"/>
       <c r="K870" s="4"/>
@@ -26100,7 +26097,7 @@
         <v>33</v>
       </c>
       <c r="B871" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C871" s="4">
         <v>46</v>
@@ -26117,7 +26114,7 @@
         <v>13</v>
       </c>
       <c r="I871" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J871" s="8"/>
       <c r="K871" s="4"/>
@@ -26127,7 +26124,7 @@
         <v>11</v>
       </c>
       <c r="B872" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C872" s="4">
         <v>345</v>
@@ -26144,7 +26141,7 @@
         <v>13</v>
       </c>
       <c r="I872" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J872" s="8">
         <v>1304</v>
@@ -26156,7 +26153,7 @@
         <v>18</v>
       </c>
       <c r="B873" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C873" s="4">
         <v>246</v>
@@ -26173,7 +26170,7 @@
         <v>13</v>
       </c>
       <c r="I873" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J873" s="8">
         <v>2067.73</v>
@@ -26185,7 +26182,7 @@
         <v>11</v>
       </c>
       <c r="B874" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C874" s="4">
         <v>153</v>
@@ -26202,13 +26199,13 @@
         <v>13</v>
       </c>
       <c r="I874" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J874" s="8">
         <v>700</v>
       </c>
       <c r="K874" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="875" customHeight="1" spans="1:11">
@@ -26216,7 +26213,7 @@
         <v>33</v>
       </c>
       <c r="B875" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C875" s="4">
         <v>131</v>
@@ -26233,11 +26230,11 @@
         <v>13</v>
       </c>
       <c r="I875" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J875" s="8"/>
       <c r="K875" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="876" customHeight="1" spans="1:11">
@@ -26245,7 +26242,7 @@
         <v>18</v>
       </c>
       <c r="B876" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C876" s="4">
         <v>55</v>
@@ -26262,7 +26259,7 @@
         <v>13</v>
       </c>
       <c r="I876" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J876" s="8">
         <v>6000</v>
@@ -26274,7 +26271,7 @@
         <v>33</v>
       </c>
       <c r="B877" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C877" s="4">
         <v>52</v>
@@ -26291,7 +26288,7 @@
         <v>13</v>
       </c>
       <c r="I877" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J877" s="8">
         <v>2200</v>
@@ -26303,7 +26300,7 @@
         <v>24</v>
       </c>
       <c r="B878" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C878" s="4">
         <v>51</v>
@@ -26320,13 +26317,13 @@
         <v>13</v>
       </c>
       <c r="I878" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J878" s="8">
         <v>10000</v>
       </c>
       <c r="K878" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="879" customHeight="1" spans="1:11">
@@ -26334,7 +26331,7 @@
         <v>20</v>
       </c>
       <c r="B879" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C879" s="4">
         <v>43</v>
@@ -26351,7 +26348,7 @@
         <v>13</v>
       </c>
       <c r="I879" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J879" s="8">
         <v>1000</v>
@@ -26363,7 +26360,7 @@
         <v>11</v>
       </c>
       <c r="B880" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C880" s="4">
         <v>14</v>
@@ -26380,13 +26377,13 @@
         <v>13</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J880" s="8">
         <v>2000</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="881" customHeight="1" spans="1:11">
@@ -26394,7 +26391,7 @@
         <v>20</v>
       </c>
       <c r="B881" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C881" s="4">
         <v>200</v>
@@ -26411,13 +26408,13 @@
         <v>13</v>
       </c>
       <c r="I881" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J881" s="8">
         <v>3024</v>
       </c>
       <c r="K881" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="882" customHeight="1" spans="1:11">
@@ -26425,7 +26422,7 @@
         <v>20</v>
       </c>
       <c r="B882" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C882" s="4">
         <v>160</v>
@@ -26442,13 +26439,13 @@
         <v>13</v>
       </c>
       <c r="I882" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J882" s="8">
         <v>840</v>
       </c>
       <c r="K882" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="883" customHeight="1" spans="1:11">
@@ -26456,7 +26453,7 @@
         <v>20</v>
       </c>
       <c r="B883" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C883" s="4">
         <v>150</v>
@@ -26473,13 +26470,13 @@
         <v>13</v>
       </c>
       <c r="I883" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J883" s="8">
         <v>1920</v>
       </c>
       <c r="K883" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="884" customHeight="1" spans="1:11">
@@ -26487,7 +26484,7 @@
         <v>20</v>
       </c>
       <c r="B884" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C884" s="4">
         <v>117</v>
@@ -26504,13 +26501,13 @@
         <v>13</v>
       </c>
       <c r="I884" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J884" s="8">
         <v>1920</v>
       </c>
       <c r="K884" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="885" customHeight="1" spans="1:11">
@@ -26518,7 +26515,7 @@
         <v>24</v>
       </c>
       <c r="B885" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C885" s="4">
         <v>250</v>
@@ -26537,7 +26534,7 @@
         <v>436</v>
       </c>
       <c r="I885" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J885" s="8"/>
       <c r="K885" s="4"/>
@@ -26547,7 +26544,7 @@
         <v>24</v>
       </c>
       <c r="B886" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C886" s="4">
         <v>199</v>
@@ -26566,7 +26563,7 @@
         <v>70</v>
       </c>
       <c r="I886" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J886" s="8"/>
       <c r="K886" s="4"/>
@@ -26576,7 +26573,7 @@
         <v>24</v>
       </c>
       <c r="B887" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C887" s="4">
         <v>365</v>
@@ -26595,7 +26592,7 @@
         <v>408</v>
       </c>
       <c r="I887" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J887" s="8">
         <v>6221</v>
@@ -26607,7 +26604,7 @@
         <v>18</v>
       </c>
       <c r="B888" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C888" s="4">
         <v>334</v>
@@ -26626,7 +26623,7 @@
         <v>408</v>
       </c>
       <c r="I888" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J888" s="8">
         <v>2930</v>
@@ -26638,7 +26635,7 @@
         <v>20</v>
       </c>
       <c r="B889" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C889" s="4">
         <v>141</v>
@@ -26655,7 +26652,7 @@
         <v>13</v>
       </c>
       <c r="I889" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J889" s="8">
         <v>6000</v>
@@ -26667,7 +26664,7 @@
         <v>18</v>
       </c>
       <c r="B890" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C890" s="4">
         <v>136</v>
@@ -26684,7 +26681,7 @@
         <v>13</v>
       </c>
       <c r="I890" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J890" s="8">
         <v>1042.68</v>
@@ -26696,7 +26693,7 @@
         <v>24</v>
       </c>
       <c r="B891" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C891" s="4">
         <v>437</v>
@@ -26708,10 +26705,10 @@
       <c r="F891" s="4"/>
       <c r="G891" s="4"/>
       <c r="H891" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I891" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J891" s="8"/>
       <c r="K891" s="4"/>
@@ -26721,7 +26718,7 @@
         <v>24</v>
       </c>
       <c r="B892" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C892" s="4">
         <v>405</v>
@@ -26736,7 +26733,7 @@
         <v>13</v>
       </c>
       <c r="I892" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J892" s="8"/>
       <c r="K892" s="4"/>
@@ -26746,7 +26743,7 @@
         <v>24</v>
       </c>
       <c r="B893" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C893" s="4">
         <v>197</v>
@@ -26763,7 +26760,7 @@
         <v>462</v>
       </c>
       <c r="I893" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J893" s="8"/>
       <c r="K893" s="4"/>
@@ -26773,7 +26770,7 @@
         <v>24</v>
       </c>
       <c r="B894" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C894" s="4">
         <v>186</v>
@@ -26788,7 +26785,7 @@
         <v>13</v>
       </c>
       <c r="I894" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J894" s="8"/>
       <c r="K894" s="4"/>
@@ -26798,7 +26795,7 @@
         <v>33</v>
       </c>
       <c r="B895" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C895" s="4">
         <v>151</v>
@@ -26813,7 +26810,7 @@
         <v>13</v>
       </c>
       <c r="I895" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J895" s="8"/>
       <c r="K895" s="4"/>
@@ -26823,7 +26820,7 @@
         <v>33</v>
       </c>
       <c r="B896" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C896" s="4">
         <v>116</v>
@@ -26838,7 +26835,7 @@
         <v>23</v>
       </c>
       <c r="I896" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J896" s="8"/>
       <c r="K896" s="4"/>
@@ -26848,7 +26845,7 @@
         <v>33</v>
       </c>
       <c r="B897" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C897" s="4">
         <v>114</v>
@@ -26863,7 +26860,7 @@
         <v>32</v>
       </c>
       <c r="I897" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J897" s="8"/>
       <c r="K897" s="4"/>
@@ -26873,7 +26870,7 @@
         <v>24</v>
       </c>
       <c r="B898" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C898" s="4">
         <v>101</v>
@@ -26888,7 +26885,7 @@
         <v>32</v>
       </c>
       <c r="I898" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J898" s="8"/>
       <c r="K898" s="4"/>
@@ -26898,7 +26895,7 @@
         <v>24</v>
       </c>
       <c r="B899" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C899" s="4">
         <v>99</v>
@@ -26913,7 +26910,7 @@
         <v>23</v>
       </c>
       <c r="I899" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J899" s="8"/>
       <c r="K899" s="4"/>
@@ -26923,7 +26920,7 @@
         <v>24</v>
       </c>
       <c r="B900" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C900" s="4">
         <v>98</v>
@@ -26938,7 +26935,7 @@
         <v>23</v>
       </c>
       <c r="I900" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J900" s="8"/>
       <c r="K900" s="4"/>
@@ -26948,7 +26945,7 @@
         <v>33</v>
       </c>
       <c r="B901" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C901" s="4">
         <v>78</v>
@@ -26963,7 +26960,7 @@
         <v>13</v>
       </c>
       <c r="I901" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J901" s="8"/>
       <c r="K901" s="4"/>
@@ -26973,7 +26970,7 @@
         <v>24</v>
       </c>
       <c r="B902" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C902" s="4">
         <v>58</v>
@@ -26985,10 +26982,10 @@
       <c r="F902" s="4"/>
       <c r="G902" s="4"/>
       <c r="H902" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I902" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J902" s="8"/>
       <c r="K902" s="4"/>
@@ -26998,7 +26995,7 @@
         <v>33</v>
       </c>
       <c r="B903" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C903" s="4">
         <v>55</v>
@@ -27013,7 +27010,7 @@
         <v>23</v>
       </c>
       <c r="I903" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J903" s="8"/>
       <c r="K903" s="4"/>
@@ -27023,7 +27020,7 @@
         <v>33</v>
       </c>
       <c r="B904" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C904" s="4">
         <v>40</v>
@@ -27038,7 +27035,7 @@
         <v>32</v>
       </c>
       <c r="I904" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J904" s="8"/>
       <c r="K904" s="4"/>
@@ -27048,7 +27045,7 @@
         <v>24</v>
       </c>
       <c r="B905" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C905" s="4">
         <v>39</v>
@@ -27063,7 +27060,7 @@
         <v>23</v>
       </c>
       <c r="I905" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J905" s="8"/>
       <c r="K905" s="4"/>
@@ -27073,7 +27070,7 @@
         <v>24</v>
       </c>
       <c r="B906" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C906" s="4">
         <v>37</v>
@@ -27088,7 +27085,7 @@
         <v>23</v>
       </c>
       <c r="I906" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J906" s="8"/>
       <c r="K906" s="4"/>
@@ -27098,7 +27095,7 @@
         <v>24</v>
       </c>
       <c r="B907" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C907" s="4">
         <v>35</v>
@@ -27113,11 +27110,11 @@
         <v>13</v>
       </c>
       <c r="I907" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J907" s="8"/>
       <c r="K907" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="908" customHeight="1" spans="1:11">
@@ -27125,7 +27122,7 @@
         <v>24</v>
       </c>
       <c r="B908" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C908" s="4">
         <v>27</v>
@@ -27140,7 +27137,7 @@
         <v>13</v>
       </c>
       <c r="I908" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J908" s="8"/>
       <c r="K908" s="4"/>
@@ -27150,7 +27147,7 @@
         <v>33</v>
       </c>
       <c r="B909" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C909" s="4">
         <v>27</v>
@@ -27165,7 +27162,7 @@
         <v>23</v>
       </c>
       <c r="I909" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J909" s="8"/>
       <c r="K909" s="4"/>
@@ -27175,7 +27172,7 @@
         <v>24</v>
       </c>
       <c r="B910" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C910" s="4">
         <v>25</v>
@@ -27190,11 +27187,11 @@
         <v>13</v>
       </c>
       <c r="I910" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J910" s="8"/>
       <c r="K910" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="911" customHeight="1" spans="1:11">
@@ -27202,7 +27199,7 @@
         <v>33</v>
       </c>
       <c r="B911" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C911" s="4">
         <v>25</v>
@@ -27217,7 +27214,7 @@
         <v>32</v>
       </c>
       <c r="I911" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J911" s="8"/>
       <c r="K911" s="4"/>
@@ -27227,7 +27224,7 @@
         <v>24</v>
       </c>
       <c r="B912" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C912" s="4">
         <v>24</v>
@@ -27242,7 +27239,7 @@
         <v>23</v>
       </c>
       <c r="I912" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J912" s="8"/>
       <c r="K912" s="4"/>
@@ -27252,7 +27249,7 @@
         <v>33</v>
       </c>
       <c r="B913" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C913" s="4">
         <v>24</v>
@@ -27267,7 +27264,7 @@
         <v>23</v>
       </c>
       <c r="I913" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J913" s="8"/>
       <c r="K913" s="4"/>
@@ -27277,7 +27274,7 @@
         <v>24</v>
       </c>
       <c r="B914" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C914" s="4">
         <v>19</v>
@@ -27292,7 +27289,7 @@
         <v>23</v>
       </c>
       <c r="I914" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J914" s="8"/>
       <c r="K914" s="4"/>
@@ -27302,7 +27299,7 @@
         <v>33</v>
       </c>
       <c r="B915" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C915" s="4">
         <v>17</v>
@@ -27317,7 +27314,7 @@
         <v>13</v>
       </c>
       <c r="I915" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J915" s="8"/>
       <c r="K915" s="4"/>
@@ -27327,7 +27324,7 @@
         <v>24</v>
       </c>
       <c r="B916" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C916" s="4">
         <v>11</v>
@@ -27342,7 +27339,7 @@
         <v>23</v>
       </c>
       <c r="I916" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J916" s="8"/>
       <c r="K916" s="4"/>
@@ -27352,7 +27349,7 @@
         <v>24</v>
       </c>
       <c r="B917" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C917" s="4">
         <v>11</v>
@@ -27367,7 +27364,7 @@
         <v>23</v>
       </c>
       <c r="I917" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J917" s="8"/>
       <c r="K917" s="4"/>
@@ -27377,7 +27374,7 @@
         <v>24</v>
       </c>
       <c r="B918" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C918" s="4">
         <v>10</v>
@@ -27392,11 +27389,11 @@
         <v>32</v>
       </c>
       <c r="I918" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J918" s="8"/>
       <c r="K918" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="919" customHeight="1" spans="1:11">
@@ -27404,7 +27401,7 @@
         <v>24</v>
       </c>
       <c r="B919" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C919" s="4">
         <v>8</v>
@@ -27419,11 +27416,11 @@
         <v>13</v>
       </c>
       <c r="I919" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J919" s="8"/>
       <c r="K919" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="920" customHeight="1" spans="1:11">
@@ -27431,7 +27428,7 @@
         <v>24</v>
       </c>
       <c r="B920" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C920" s="4">
         <v>7</v>
@@ -27446,7 +27443,7 @@
         <v>23</v>
       </c>
       <c r="I920" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J920" s="8"/>
       <c r="K920" s="4"/>
@@ -27456,7 +27453,7 @@
         <v>24</v>
       </c>
       <c r="B921" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C921" s="4">
         <v>5</v>
@@ -27468,10 +27465,10 @@
       <c r="F921" s="4"/>
       <c r="G921" s="4"/>
       <c r="H921" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I921" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J921" s="8"/>
       <c r="K921" s="4"/>
@@ -27481,7 +27478,7 @@
         <v>33</v>
       </c>
       <c r="B922" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C922" s="4">
         <v>5</v>
@@ -27496,7 +27493,7 @@
         <v>23</v>
       </c>
       <c r="I922" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J922" s="8"/>
       <c r="K922" s="4"/>
@@ -27506,7 +27503,7 @@
         <v>24</v>
       </c>
       <c r="B923" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C923" s="4">
         <v>4</v>
@@ -27521,7 +27518,7 @@
         <v>23</v>
       </c>
       <c r="I923" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J923" s="8"/>
       <c r="K923" s="4"/>
@@ -27531,7 +27528,7 @@
         <v>24</v>
       </c>
       <c r="B924" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C924" s="4">
         <v>4</v>
@@ -27546,7 +27543,7 @@
         <v>13</v>
       </c>
       <c r="I924" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J924" s="8"/>
       <c r="K924" s="4"/>
@@ -27556,7 +27553,7 @@
         <v>24</v>
       </c>
       <c r="B925" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C925" s="4">
         <v>4</v>
@@ -27571,7 +27568,7 @@
         <v>13</v>
       </c>
       <c r="I925" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J925" s="8"/>
       <c r="K925" s="4"/>
@@ -27581,7 +27578,7 @@
         <v>24</v>
       </c>
       <c r="B926" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C926" s="4">
         <v>3</v>
@@ -27594,11 +27591,11 @@
       <c r="G926" s="4"/>
       <c r="H926" s="4"/>
       <c r="I926" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J926" s="8"/>
       <c r="K926" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="927" customHeight="1" spans="1:11">
@@ -27606,7 +27603,7 @@
         <v>24</v>
       </c>
       <c r="B927" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C927" s="4">
         <v>2</v>
@@ -27619,11 +27616,11 @@
       <c r="G927" s="4"/>
       <c r="H927" s="4"/>
       <c r="I927" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J927" s="8"/>
       <c r="K927" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="928" customHeight="1" spans="1:11">
@@ -27631,7 +27628,7 @@
         <v>24</v>
       </c>
       <c r="B928" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C928" s="4">
         <v>1</v>
@@ -27646,7 +27643,7 @@
         <v>13</v>
       </c>
       <c r="I928" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J928" s="8"/>
       <c r="K928" s="4"/>
@@ -27656,7 +27653,7 @@
         <v>24</v>
       </c>
       <c r="B929" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C929" s="12"/>
       <c r="D929" s="12"/>
@@ -27665,7 +27662,7 @@
       <c r="G929" s="12"/>
       <c r="H929" s="13"/>
       <c r="I929" s="12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J929" s="14">
         <v>51740.34</v>
@@ -27677,7 +27674,7 @@
         <v>33</v>
       </c>
       <c r="B930" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C930" s="12"/>
       <c r="D930" s="12"/>
@@ -27686,7 +27683,7 @@
       <c r="G930" s="12"/>
       <c r="H930" s="13"/>
       <c r="I930" s="12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J930" s="14">
         <v>22552.29</v>
@@ -27698,7 +27695,7 @@
         <v>18</v>
       </c>
       <c r="B931" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C931" s="12"/>
       <c r="D931" s="12"/>
@@ -27707,7 +27704,7 @@
       <c r="G931" s="12"/>
       <c r="H931" s="13"/>
       <c r="I931" s="12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J931" s="14">
         <v>17326.35</v>
@@ -27719,7 +27716,7 @@
         <v>33</v>
       </c>
       <c r="B932" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C932" s="4">
         <v>2018</v>
@@ -27736,7 +27733,7 @@
         <v>462</v>
       </c>
       <c r="I932" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J932" s="8">
         <v>34675</v>
@@ -27748,7 +27745,7 @@
         <v>33</v>
       </c>
       <c r="B933" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C933" s="4">
         <v>1525</v>
@@ -27765,11 +27762,11 @@
         <v>462</v>
       </c>
       <c r="I933" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J933" s="8"/>
       <c r="K933" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="934" customHeight="1" spans="1:11">
@@ -27777,7 +27774,7 @@
         <v>33</v>
       </c>
       <c r="B934" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C934" s="4">
         <v>1117</v>
@@ -27794,7 +27791,7 @@
         <v>462</v>
       </c>
       <c r="I934" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J934" s="8">
         <v>33020</v>
@@ -27806,7 +27803,7 @@
         <v>18</v>
       </c>
       <c r="B935" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C935" s="4">
         <v>852</v>
@@ -27823,7 +27820,7 @@
         <v>462</v>
       </c>
       <c r="I935" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J935" s="8">
         <v>8500</v>
@@ -27835,7 +27832,7 @@
         <v>20</v>
       </c>
       <c r="B936" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C936" s="4">
         <v>612</v>
@@ -27852,13 +27849,13 @@
         <v>462</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J936" s="8">
         <v>16000</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="937" customHeight="1" spans="1:11">
@@ -27866,7 +27863,7 @@
         <v>18</v>
       </c>
       <c r="B937" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C937" s="4">
         <v>597</v>
@@ -27883,7 +27880,7 @@
         <v>462</v>
       </c>
       <c r="I937" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J937" s="8">
         <v>32392</v>
@@ -27895,7 +27892,7 @@
         <v>33</v>
       </c>
       <c r="B938" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C938" s="4">
         <v>529</v>
@@ -27910,7 +27907,7 @@
         <v>13</v>
       </c>
       <c r="I938" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J938" s="8">
         <v>12461</v>
@@ -27922,7 +27919,7 @@
         <v>33</v>
       </c>
       <c r="B939" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C939" s="4">
         <v>511</v>
@@ -27939,7 +27936,7 @@
         <v>785</v>
       </c>
       <c r="I939" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J939" s="8">
         <v>38400</v>
@@ -27951,7 +27948,7 @@
         <v>18</v>
       </c>
       <c r="B940" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C940" s="4">
         <v>492</v>
@@ -27963,10 +27960,10 @@
       <c r="F940" s="4"/>
       <c r="G940" s="4"/>
       <c r="H940" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I940" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J940" s="8">
         <v>7420</v>
@@ -27978,7 +27975,7 @@
         <v>24</v>
       </c>
       <c r="B941" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C941" s="4">
         <v>457</v>
@@ -27992,10 +27989,10 @@
       <c r="F941" s="4"/>
       <c r="G941" s="4"/>
       <c r="H941" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="I941" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J941" s="8">
         <v>16779.6</v>
@@ -28007,7 +28004,7 @@
         <v>20</v>
       </c>
       <c r="B942" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C942" s="4">
         <v>347</v>
@@ -28024,7 +28021,7 @@
         <v>462</v>
       </c>
       <c r="I942" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J942" s="8">
         <v>14729</v>
@@ -28036,7 +28033,7 @@
         <v>33</v>
       </c>
       <c r="B943" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C943" s="4">
         <v>216</v>
@@ -28051,7 +28048,7 @@
         <v>13</v>
       </c>
       <c r="I943" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J943" s="8">
         <v>1000</v>
@@ -28063,7 +28060,7 @@
         <v>18</v>
       </c>
       <c r="B944" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C944" s="4">
         <v>204</v>
@@ -28078,7 +28075,7 @@
         <v>23</v>
       </c>
       <c r="I944" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J944" s="8">
         <v>8066.75</v>
@@ -28090,7 +28087,7 @@
         <v>18</v>
       </c>
       <c r="B945" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C945" s="4">
         <v>180</v>
@@ -28105,7 +28102,7 @@
         <v>32</v>
       </c>
       <c r="I945" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J945" s="8">
         <v>6000</v>
@@ -28117,7 +28114,7 @@
         <v>24</v>
       </c>
       <c r="B946" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C946" s="4">
         <v>164</v>
@@ -28132,7 +28129,7 @@
         <v>32</v>
       </c>
       <c r="I946" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J946" s="8">
         <v>10800</v>
@@ -28144,7 +28141,7 @@
         <v>24</v>
       </c>
       <c r="B947" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C947" s="4">
         <v>158</v>
@@ -28157,7 +28154,7 @@
       <c r="G947" s="4"/>
       <c r="H947" s="4"/>
       <c r="I947" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J947" s="8">
         <v>2927</v>
@@ -28169,7 +28166,7 @@
         <v>18</v>
       </c>
       <c r="B948" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C948" s="4">
         <v>155</v>
@@ -28186,7 +28183,7 @@
         <v>436</v>
       </c>
       <c r="I948" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J948" s="8">
         <v>6574</v>
@@ -28198,7 +28195,7 @@
         <v>18</v>
       </c>
       <c r="B949" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C949" s="4">
         <v>152</v>
@@ -28213,7 +28210,7 @@
         <v>32</v>
       </c>
       <c r="I949" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J949" s="8">
         <v>5800</v>
@@ -28225,7 +28222,7 @@
         <v>18</v>
       </c>
       <c r="B950" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C950" s="4">
         <v>150</v>
@@ -28242,7 +28239,7 @@
         <v>462</v>
       </c>
       <c r="I950" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J950" s="8">
         <v>7631</v>
@@ -28254,7 +28251,7 @@
         <v>20</v>
       </c>
       <c r="B951" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C951" s="4">
         <v>137</v>
@@ -28269,7 +28266,7 @@
         <v>23</v>
       </c>
       <c r="I951" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J951" s="8">
         <v>3698</v>
@@ -28281,7 +28278,7 @@
         <v>33</v>
       </c>
       <c r="B952" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C952" s="4">
         <v>136</v>
@@ -28296,7 +28293,7 @@
         <v>13</v>
       </c>
       <c r="I952" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J952" s="8"/>
       <c r="K952" s="4"/>
@@ -28306,7 +28303,7 @@
         <v>20</v>
       </c>
       <c r="B953" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C953" s="4">
         <v>135</v>
@@ -28323,7 +28320,7 @@
         <v>785</v>
       </c>
       <c r="I953" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J953" s="8">
         <v>20000</v>
@@ -28335,7 +28332,7 @@
         <v>11</v>
       </c>
       <c r="B954" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C954" s="4">
         <v>133</v>
@@ -28350,7 +28347,7 @@
         <v>13</v>
       </c>
       <c r="I954" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J954" s="8">
         <v>1600</v>
@@ -28362,7 +28359,7 @@
         <v>33</v>
       </c>
       <c r="B955" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C955" s="4">
         <v>133</v>
@@ -28379,7 +28376,7 @@
         <v>462</v>
       </c>
       <c r="I955" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J955" s="8">
         <v>7200</v>
@@ -28391,7 +28388,7 @@
         <v>33</v>
       </c>
       <c r="B956" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C956" s="4">
         <v>133</v>
@@ -28406,7 +28403,7 @@
         <v>13</v>
       </c>
       <c r="I956" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J956" s="8">
         <v>2830</v>
@@ -28418,7 +28415,7 @@
         <v>33</v>
       </c>
       <c r="B957" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C957" s="4">
         <v>131</v>
@@ -28433,7 +28430,7 @@
         <v>13</v>
       </c>
       <c r="I957" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J957" s="8">
         <v>1673</v>
@@ -28445,7 +28442,7 @@
         <v>11</v>
       </c>
       <c r="B958" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C958" s="4">
         <v>126</v>
@@ -28460,11 +28457,11 @@
         <v>13</v>
       </c>
       <c r="I958" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J958" s="8"/>
       <c r="K958" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="959" customHeight="1" spans="1:11">
@@ -28472,7 +28469,7 @@
         <v>18</v>
       </c>
       <c r="B959" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C959" s="4">
         <v>116</v>
@@ -28487,7 +28484,7 @@
         <v>13</v>
       </c>
       <c r="I959" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J959" s="8">
         <v>1508.06</v>
@@ -28499,7 +28496,7 @@
         <v>18</v>
       </c>
       <c r="B960" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C960" s="4">
         <v>115</v>
@@ -28516,7 +28513,7 @@
         <v>462</v>
       </c>
       <c r="I960" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J960" s="8">
         <v>11000</v>
@@ -28528,7 +28525,7 @@
         <v>18</v>
       </c>
       <c r="B961" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C961" s="4">
         <v>115</v>
@@ -28543,7 +28540,7 @@
         <v>23</v>
       </c>
       <c r="I961" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J961" s="8">
         <v>2849</v>
@@ -28555,7 +28552,7 @@
         <v>24</v>
       </c>
       <c r="B962" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C962" s="4">
         <v>114</v>
@@ -28570,11 +28567,11 @@
         <v>23</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J962" s="8"/>
       <c r="K962" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="963" customHeight="1" spans="1:11">
@@ -28582,7 +28579,7 @@
         <v>18</v>
       </c>
       <c r="B963" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C963" s="4">
         <v>114</v>
@@ -28597,11 +28594,11 @@
         <v>462</v>
       </c>
       <c r="I963" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J963" s="8"/>
       <c r="K963" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="964" customHeight="1" spans="1:11">
@@ -28609,7 +28606,7 @@
         <v>18</v>
       </c>
       <c r="B964" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C964" s="4">
         <v>110</v>
@@ -28624,13 +28621,13 @@
         <v>13</v>
       </c>
       <c r="I964" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J964" s="8">
         <v>6808.46</v>
       </c>
       <c r="K964" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="965" customHeight="1" spans="1:11">
@@ -28638,7 +28635,7 @@
         <v>20</v>
       </c>
       <c r="B965" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C965" s="4">
         <v>110</v>
@@ -28653,7 +28650,7 @@
         <v>23</v>
       </c>
       <c r="I965" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J965" s="8">
         <v>3965</v>
@@ -28665,7 +28662,7 @@
         <v>18</v>
       </c>
       <c r="B966" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C966" s="4">
         <v>109</v>
@@ -28680,7 +28677,7 @@
         <v>484</v>
       </c>
       <c r="I966" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J966" s="8">
         <v>163.03</v>
@@ -28692,7 +28689,7 @@
         <v>18</v>
       </c>
       <c r="B967" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C967" s="4">
         <v>106</v>
@@ -28709,7 +28706,7 @@
         <v>462</v>
       </c>
       <c r="I967" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J967" s="8">
         <v>3552</v>
@@ -28721,7 +28718,7 @@
         <v>20</v>
       </c>
       <c r="B968" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C968" s="4">
         <v>106</v>
@@ -28736,7 +28733,7 @@
         <v>23</v>
       </c>
       <c r="I968" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J968" s="8">
         <v>7500</v>
@@ -28748,7 +28745,7 @@
         <v>18</v>
       </c>
       <c r="B969" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C969" s="4">
         <v>101</v>
@@ -28765,7 +28762,7 @@
         <v>462</v>
       </c>
       <c r="I969" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J969" s="8">
         <v>8865</v>
@@ -28777,7 +28774,7 @@
         <v>11</v>
       </c>
       <c r="B970" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C970" s="4">
         <v>100</v>
@@ -28792,7 +28789,7 @@
         <v>13</v>
       </c>
       <c r="I970" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J970" s="8">
         <v>1500</v>
@@ -28804,7 +28801,7 @@
         <v>18</v>
       </c>
       <c r="B971" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C971" s="4">
         <v>100</v>
@@ -28819,7 +28816,7 @@
         <v>32</v>
       </c>
       <c r="I971" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J971" s="8">
         <v>20880</v>
@@ -28831,7 +28828,7 @@
         <v>11</v>
       </c>
       <c r="B972" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C972" s="4">
         <v>87</v>
@@ -28846,11 +28843,11 @@
         <v>13</v>
       </c>
       <c r="I972" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J972" s="8"/>
       <c r="K972" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="973" customHeight="1" spans="1:11">
@@ -28858,7 +28855,7 @@
         <v>33</v>
       </c>
       <c r="B973" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C973" s="4">
         <v>87</v>
@@ -28873,7 +28870,7 @@
         <v>23</v>
       </c>
       <c r="I973" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J973" s="8">
         <v>4573</v>
@@ -28885,7 +28882,7 @@
         <v>20</v>
       </c>
       <c r="B974" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C974" s="4">
         <v>87</v>
@@ -28902,11 +28899,11 @@
         <v>462</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J974" s="8"/>
       <c r="K974" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="975" customHeight="1" spans="1:11">
@@ -28914,7 +28911,7 @@
         <v>11</v>
       </c>
       <c r="B975" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C975" s="4">
         <v>85</v>
@@ -28929,7 +28926,7 @@
         <v>13</v>
       </c>
       <c r="I975" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J975" s="8">
         <v>4000</v>
@@ -28941,7 +28938,7 @@
         <v>11</v>
       </c>
       <c r="B976" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C976" s="4">
         <v>80</v>
@@ -28956,7 +28953,7 @@
         <v>13</v>
       </c>
       <c r="I976" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J976" s="8">
         <v>4345</v>
@@ -28968,7 +28965,7 @@
         <v>33</v>
       </c>
       <c r="B977" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C977" s="4">
         <v>79</v>
@@ -28983,11 +28980,11 @@
         <v>13</v>
       </c>
       <c r="I977" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J977" s="8"/>
       <c r="K977" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="978" customHeight="1" spans="1:11">
@@ -28995,7 +28992,7 @@
         <v>24</v>
       </c>
       <c r="B978" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C978" s="4">
         <v>76</v>
@@ -29010,7 +29007,7 @@
         <v>13</v>
       </c>
       <c r="I978" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J978" s="8">
         <v>13806</v>
@@ -29022,7 +29019,7 @@
         <v>18</v>
       </c>
       <c r="B979" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C979" s="4">
         <v>74</v>
@@ -29039,13 +29036,13 @@
         <v>462</v>
       </c>
       <c r="I979" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J979" s="8">
         <v>4544</v>
       </c>
       <c r="K979" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="980" customHeight="1" spans="1:11">
@@ -29053,7 +29050,7 @@
         <v>11</v>
       </c>
       <c r="B980" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C980" s="4">
         <v>71</v>
@@ -29068,7 +29065,7 @@
         <v>13</v>
       </c>
       <c r="I980" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J980" s="8">
         <v>768.71</v>
@@ -29080,7 +29077,7 @@
         <v>18</v>
       </c>
       <c r="B981" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C981" s="4">
         <v>68</v>
@@ -29095,7 +29092,7 @@
         <v>13</v>
       </c>
       <c r="I981" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J981" s="8">
         <v>361.96</v>
@@ -29107,7 +29104,7 @@
         <v>24</v>
       </c>
       <c r="B982" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C982" s="4">
         <v>67</v>
@@ -29124,7 +29121,7 @@
         <v>462</v>
       </c>
       <c r="I982" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J982" s="8">
         <v>2800</v>
@@ -29136,7 +29133,7 @@
         <v>18</v>
       </c>
       <c r="B983" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C983" s="4">
         <v>67</v>
@@ -29151,7 +29148,7 @@
         <v>436</v>
       </c>
       <c r="I983" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J983" s="8">
         <v>945.96</v>
@@ -29163,7 +29160,7 @@
         <v>11</v>
       </c>
       <c r="B984" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C984" s="4">
         <v>66</v>
@@ -29178,7 +29175,7 @@
         <v>13</v>
       </c>
       <c r="I984" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J984" s="8">
         <v>4000</v>
@@ -29190,7 +29187,7 @@
         <v>20</v>
       </c>
       <c r="B985" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C985" s="4">
         <v>66</v>
@@ -29203,7 +29200,7 @@
       <c r="G985" s="4"/>
       <c r="H985" s="4"/>
       <c r="I985" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J985" s="8">
         <v>522</v>
@@ -29215,7 +29212,7 @@
         <v>33</v>
       </c>
       <c r="B986" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C986" s="4">
         <v>64</v>
@@ -29230,13 +29227,13 @@
         <v>32</v>
       </c>
       <c r="I986" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J986" s="8">
         <v>2955.34</v>
       </c>
       <c r="K986" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="987" customHeight="1" spans="1:11">
@@ -29244,7 +29241,7 @@
         <v>18</v>
       </c>
       <c r="B987" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C987" s="4">
         <v>64</v>
@@ -29259,7 +29256,7 @@
         <v>23</v>
       </c>
       <c r="I987" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J987" s="8">
         <v>4927</v>
@@ -29271,7 +29268,7 @@
         <v>11</v>
       </c>
       <c r="B988" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C988" s="4">
         <v>59</v>
@@ -29286,11 +29283,11 @@
         <v>13</v>
       </c>
       <c r="I988" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J988" s="8"/>
       <c r="K988" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="989" customHeight="1" spans="1:11">
@@ -29298,7 +29295,7 @@
         <v>20</v>
       </c>
       <c r="B989" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C989" s="4">
         <v>58</v>
@@ -29315,7 +29312,7 @@
         <v>462</v>
       </c>
       <c r="I989" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J989" s="8">
         <v>1980</v>
@@ -29327,7 +29324,7 @@
         <v>20</v>
       </c>
       <c r="B990" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C990" s="4">
         <v>57</v>
@@ -29342,7 +29339,7 @@
         <v>23</v>
       </c>
       <c r="I990" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J990" s="8">
         <v>1765</v>
@@ -29354,7 +29351,7 @@
         <v>24</v>
       </c>
       <c r="B991" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C991" s="4">
         <v>56</v>
@@ -29369,7 +29366,7 @@
         <v>23</v>
       </c>
       <c r="I991" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J991" s="8">
         <v>2875</v>
@@ -29381,7 +29378,7 @@
         <v>18</v>
       </c>
       <c r="B992" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C992" s="4">
         <v>56</v>
@@ -29396,7 +29393,7 @@
         <v>32</v>
       </c>
       <c r="I992" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J992" s="8">
         <v>1200</v>
@@ -29408,7 +29405,7 @@
         <v>11</v>
       </c>
       <c r="B993" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C993" s="4">
         <v>53</v>
@@ -29423,11 +29420,11 @@
         <v>13</v>
       </c>
       <c r="I993" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J993" s="8"/>
       <c r="K993" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="994" customHeight="1" spans="1:11">
@@ -29435,7 +29432,7 @@
         <v>20</v>
       </c>
       <c r="B994" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C994" s="4">
         <v>52</v>
@@ -29450,11 +29447,11 @@
         <v>32</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J994" s="8"/>
       <c r="K994" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="995" customHeight="1" spans="1:11">
@@ -29462,7 +29459,7 @@
         <v>20</v>
       </c>
       <c r="B995" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C995" s="4">
         <v>51</v>
@@ -29477,7 +29474,7 @@
         <v>227</v>
       </c>
       <c r="I995" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J995" s="8">
         <v>1850</v>
@@ -29489,7 +29486,7 @@
         <v>18</v>
       </c>
       <c r="B996" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C996" s="4">
         <v>50</v>
@@ -29502,7 +29499,7 @@
       <c r="G996" s="4"/>
       <c r="H996" s="4"/>
       <c r="I996" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J996" s="8">
         <v>1075.54</v>
@@ -29514,7 +29511,7 @@
         <v>18</v>
       </c>
       <c r="B997" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C997" s="4">
         <v>50</v>
@@ -29529,7 +29526,7 @@
         <v>32</v>
       </c>
       <c r="I997" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J997" s="8">
         <v>80</v>
@@ -29541,7 +29538,7 @@
         <v>18</v>
       </c>
       <c r="B998" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C998" s="4">
         <v>49</v>
@@ -29556,7 +29553,7 @@
         <v>13</v>
       </c>
       <c r="I998" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J998" s="8">
         <v>3437.5</v>
@@ -29568,7 +29565,7 @@
         <v>11</v>
       </c>
       <c r="B999" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C999" s="4">
         <v>47</v>
@@ -29583,7 +29580,7 @@
         <v>13</v>
       </c>
       <c r="I999" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J999" s="8">
         <v>1000</v>
@@ -29595,7 +29592,7 @@
         <v>33</v>
       </c>
       <c r="B1000" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C1000" s="4">
         <v>47</v>
@@ -29610,7 +29607,7 @@
         <v>13</v>
       </c>
       <c r="I1000" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1000" s="8">
         <v>1200</v>
@@ -29622,7 +29619,7 @@
         <v>20</v>
       </c>
       <c r="B1001" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C1001" s="4">
         <v>47</v>
@@ -29637,7 +29634,7 @@
         <v>23</v>
       </c>
       <c r="I1001" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1001" s="8">
         <v>432</v>
@@ -29649,7 +29646,7 @@
         <v>18</v>
       </c>
       <c r="B1002" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C1002" s="4">
         <v>43</v>
@@ -29664,7 +29661,7 @@
         <v>32</v>
       </c>
       <c r="I1002" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1002" s="8">
         <v>5112</v>
@@ -29676,7 +29673,7 @@
         <v>18</v>
       </c>
       <c r="B1003" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C1003" s="4">
         <v>42</v>
@@ -29691,7 +29688,7 @@
         <v>32</v>
       </c>
       <c r="I1003" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1003" s="8">
         <v>68</v>
@@ -29703,7 +29700,7 @@
         <v>24</v>
       </c>
       <c r="B1004" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C1004" s="4">
         <v>40</v>
@@ -29720,7 +29717,7 @@
         <v>462</v>
       </c>
       <c r="I1004" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1004" s="8">
         <v>3600</v>
@@ -29732,7 +29729,7 @@
         <v>20</v>
       </c>
       <c r="B1005" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C1005" s="4">
         <v>39</v>
@@ -29745,7 +29742,7 @@
       <c r="G1005" s="4"/>
       <c r="H1005" s="4"/>
       <c r="I1005" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1005" s="8">
         <v>1804</v>
@@ -29757,7 +29754,7 @@
         <v>33</v>
       </c>
       <c r="B1006" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C1006" s="4">
         <v>37</v>
@@ -29770,7 +29767,7 @@
       <c r="G1006" s="4"/>
       <c r="H1006" s="4"/>
       <c r="I1006" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1006" s="8">
         <v>2240</v>
@@ -29782,7 +29779,7 @@
         <v>33</v>
       </c>
       <c r="B1007" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C1007" s="4">
         <v>36</v>
@@ -29797,7 +29794,7 @@
         <v>32</v>
       </c>
       <c r="I1007" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1007" s="8">
         <v>3719</v>
@@ -29809,7 +29806,7 @@
         <v>18</v>
       </c>
       <c r="B1008" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C1008" s="4">
         <v>36</v>
@@ -29824,7 +29821,7 @@
         <v>23</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1008" s="8">
         <v>1930.85</v>
@@ -29836,7 +29833,7 @@
         <v>11</v>
       </c>
       <c r="B1009" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C1009" s="4">
         <v>35</v>
@@ -29851,11 +29848,11 @@
         <v>13</v>
       </c>
       <c r="I1009" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1009" s="8"/>
       <c r="K1009" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1010" customHeight="1" spans="1:11">
@@ -29863,7 +29860,7 @@
         <v>24</v>
       </c>
       <c r="B1010" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C1010" s="4">
         <v>35</v>
@@ -29878,7 +29875,7 @@
         <v>13</v>
       </c>
       <c r="I1010" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1010" s="8">
         <v>2509</v>
@@ -29890,7 +29887,7 @@
         <v>11</v>
       </c>
       <c r="B1011" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C1011" s="4">
         <v>34</v>
@@ -29905,7 +29902,7 @@
         <v>32</v>
       </c>
       <c r="I1011" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1011" s="8">
         <v>1300</v>
@@ -29917,7 +29914,7 @@
         <v>20</v>
       </c>
       <c r="B1012" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C1012" s="4">
         <v>33</v>
@@ -29932,7 +29929,7 @@
         <v>23</v>
       </c>
       <c r="I1012" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1012" s="8">
         <v>2000</v>
@@ -29944,7 +29941,7 @@
         <v>18</v>
       </c>
       <c r="B1013" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C1013" s="4">
         <v>32</v>
@@ -29959,7 +29956,7 @@
         <v>23</v>
       </c>
       <c r="I1013" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1013" s="8">
         <v>1936</v>
@@ -29971,7 +29968,7 @@
         <v>24</v>
       </c>
       <c r="B1014" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C1014" s="4">
         <v>31</v>
@@ -29988,7 +29985,7 @@
         <v>436</v>
       </c>
       <c r="I1014" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1014" s="8">
         <v>10635</v>
@@ -30000,7 +29997,7 @@
         <v>33</v>
       </c>
       <c r="B1015" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C1015" s="4">
         <v>30</v>
@@ -30017,13 +30014,13 @@
         <v>436</v>
       </c>
       <c r="I1015" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1015" s="8">
         <v>8513</v>
       </c>
       <c r="K1015" s="4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1016" customHeight="1" spans="1:11">
@@ -30031,7 +30028,7 @@
         <v>11</v>
       </c>
       <c r="B1016" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C1016" s="4">
         <v>28</v>
@@ -30046,11 +30043,11 @@
         <v>13</v>
       </c>
       <c r="I1016" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1016" s="8"/>
       <c r="K1016" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1017" customHeight="1" spans="1:11">
@@ -30058,7 +30055,7 @@
         <v>33</v>
       </c>
       <c r="B1017" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C1017" s="4">
         <v>28</v>
@@ -30073,7 +30070,7 @@
         <v>23</v>
       </c>
       <c r="I1017" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1017" s="8">
         <v>815</v>
@@ -30085,7 +30082,7 @@
         <v>18</v>
       </c>
       <c r="B1018" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C1018" s="4">
         <v>28</v>
@@ -30102,7 +30099,7 @@
         <v>436</v>
       </c>
       <c r="I1018" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1018" s="8">
         <v>3000</v>
@@ -30114,7 +30111,7 @@
         <v>33</v>
       </c>
       <c r="B1019" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C1019" s="4">
         <v>27</v>
@@ -30129,7 +30126,7 @@
         <v>13</v>
       </c>
       <c r="I1019" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1019" s="8">
         <v>937</v>
@@ -30141,7 +30138,7 @@
         <v>11</v>
       </c>
       <c r="B1020" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C1020" s="4">
         <v>26</v>
@@ -30156,11 +30153,11 @@
         <v>13</v>
       </c>
       <c r="I1020" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1020" s="8"/>
       <c r="K1020" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1021" customHeight="1" spans="1:11">
@@ -30168,7 +30165,7 @@
         <v>33</v>
       </c>
       <c r="B1021" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C1021" s="4">
         <v>26</v>
@@ -30183,7 +30180,7 @@
         <v>13</v>
       </c>
       <c r="I1021" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1021" s="8"/>
       <c r="K1021" s="4"/>
@@ -30193,7 +30190,7 @@
         <v>18</v>
       </c>
       <c r="B1022" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C1022" s="4">
         <v>26</v>
@@ -30208,7 +30205,7 @@
         <v>23</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1022" s="8">
         <v>2800</v>
@@ -30220,7 +30217,7 @@
         <v>20</v>
       </c>
       <c r="B1023" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C1023" s="4">
         <v>26</v>
@@ -30235,11 +30232,11 @@
         <v>23</v>
       </c>
       <c r="I1023" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1023" s="8"/>
       <c r="K1023" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1024" customHeight="1" spans="1:11">
@@ -30247,7 +30244,7 @@
         <v>20</v>
       </c>
       <c r="B1024" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C1024" s="4">
         <v>26</v>
@@ -30262,7 +30259,7 @@
         <v>23</v>
       </c>
       <c r="I1024" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1024" s="8">
         <v>12036</v>
@@ -30274,7 +30271,7 @@
         <v>11</v>
       </c>
       <c r="B1025" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C1025" s="4">
         <v>25</v>
@@ -30289,11 +30286,11 @@
         <v>13</v>
       </c>
       <c r="I1025" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1025" s="8"/>
       <c r="K1025" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1026" customHeight="1" spans="1:11">
@@ -30301,7 +30298,7 @@
         <v>33</v>
       </c>
       <c r="B1026" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C1026" s="4">
         <v>25</v>
@@ -30314,7 +30311,7 @@
       <c r="G1026" s="4"/>
       <c r="H1026" s="4"/>
       <c r="I1026" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1026" s="8">
         <v>1200</v>
@@ -30326,7 +30323,7 @@
         <v>18</v>
       </c>
       <c r="B1027" s="3" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C1027" s="4">
         <v>25</v>
@@ -30341,7 +30338,7 @@
         <v>23</v>
       </c>
       <c r="I1027" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1027" s="8">
         <v>1766</v>
@@ -30353,7 +30350,7 @@
         <v>20</v>
       </c>
       <c r="B1028" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C1028" s="4">
         <v>25</v>
@@ -30370,13 +30367,13 @@
         <v>436</v>
       </c>
       <c r="I1028" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1028" s="8">
         <v>5500</v>
       </c>
       <c r="K1028" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1029" customHeight="1" spans="1:11">
@@ -30384,7 +30381,7 @@
         <v>20</v>
       </c>
       <c r="B1029" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C1029" s="4">
         <v>25</v>
@@ -30399,7 +30396,7 @@
         <v>23</v>
       </c>
       <c r="I1029" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1029" s="8">
         <v>2908</v>
@@ -30411,7 +30408,7 @@
         <v>11</v>
       </c>
       <c r="B1030" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C1030" s="4">
         <v>24</v>
@@ -30426,11 +30423,11 @@
         <v>32</v>
       </c>
       <c r="I1030" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1030" s="8"/>
       <c r="K1030" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="1031" customHeight="1" spans="1:11">
@@ -30438,7 +30435,7 @@
         <v>11</v>
       </c>
       <c r="B1031" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C1031" s="4">
         <v>24</v>
@@ -30453,7 +30450,7 @@
         <v>13</v>
       </c>
       <c r="I1031" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1031" s="8">
         <v>5900</v>
@@ -30465,7 +30462,7 @@
         <v>33</v>
       </c>
       <c r="B1032" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C1032" s="4">
         <v>24</v>
@@ -30480,13 +30477,13 @@
         <v>13</v>
       </c>
       <c r="I1032" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1032" s="8">
         <v>22298.76</v>
       </c>
       <c r="K1032" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1033" customHeight="1" spans="1:11">
@@ -30494,7 +30491,7 @@
         <v>20</v>
       </c>
       <c r="B1033" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C1033" s="4">
         <v>23</v>
@@ -30509,7 +30506,7 @@
         <v>23</v>
       </c>
       <c r="I1033" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1033" s="8">
         <v>1923</v>
@@ -30521,7 +30518,7 @@
         <v>18</v>
       </c>
       <c r="B1034" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C1034" s="4">
         <v>22</v>
@@ -30536,7 +30533,7 @@
         <v>23</v>
       </c>
       <c r="I1034" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1034" s="8">
         <v>1500</v>
@@ -30548,7 +30545,7 @@
         <v>20</v>
       </c>
       <c r="B1035" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C1035" s="4">
         <v>20</v>
@@ -30561,7 +30558,7 @@
       <c r="G1035" s="4"/>
       <c r="H1035" s="4"/>
       <c r="I1035" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1035" s="8">
         <v>1693</v>
@@ -30573,7 +30570,7 @@
         <v>20</v>
       </c>
       <c r="B1036" s="3" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C1036" s="4">
         <v>19</v>
@@ -30588,7 +30585,7 @@
         <v>23</v>
       </c>
       <c r="I1036" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1036" s="8"/>
       <c r="K1036" s="4"/>
@@ -30598,7 +30595,7 @@
         <v>20</v>
       </c>
       <c r="B1037" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C1037" s="4">
         <v>18</v>
@@ -30615,11 +30612,11 @@
         <v>436</v>
       </c>
       <c r="I1037" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1037" s="8"/>
       <c r="K1037" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1038" customHeight="1" spans="1:11">
@@ -30627,7 +30624,7 @@
         <v>11</v>
       </c>
       <c r="B1038" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C1038" s="4">
         <v>17</v>
@@ -30642,11 +30639,11 @@
         <v>13</v>
       </c>
       <c r="I1038" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1038" s="8"/>
       <c r="K1038" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1039" customHeight="1" spans="1:11">
@@ -30654,7 +30651,7 @@
         <v>11</v>
       </c>
       <c r="B1039" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C1039" s="4">
         <v>17</v>
@@ -30669,7 +30666,7 @@
         <v>23</v>
       </c>
       <c r="I1039" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1039" s="8">
         <v>200</v>
@@ -30681,7 +30678,7 @@
         <v>33</v>
       </c>
       <c r="B1040" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C1040" s="4">
         <v>17</v>
@@ -30696,11 +30693,11 @@
         <v>32</v>
       </c>
       <c r="I1040" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1040" s="8"/>
       <c r="K1040" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="1041" customHeight="1" spans="1:11">
@@ -30708,7 +30705,7 @@
         <v>24</v>
       </c>
       <c r="B1041" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C1041" s="4">
         <v>15</v>
@@ -30725,11 +30722,11 @@
         <v>462</v>
       </c>
       <c r="I1041" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1041" s="8"/>
       <c r="K1041" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1042" customHeight="1" spans="1:11">
@@ -30737,7 +30734,7 @@
         <v>33</v>
       </c>
       <c r="B1042" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C1042" s="4">
         <v>15</v>
@@ -30752,7 +30749,7 @@
         <v>23</v>
       </c>
       <c r="I1042" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1042" s="8">
         <v>1934</v>
@@ -30764,7 +30761,7 @@
         <v>18</v>
       </c>
       <c r="B1043" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C1043" s="4">
         <v>15</v>
@@ -30779,7 +30776,7 @@
         <v>23</v>
       </c>
       <c r="I1043" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1043" s="8">
         <v>1760</v>
@@ -30791,7 +30788,7 @@
         <v>11</v>
       </c>
       <c r="B1044" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C1044" s="4">
         <v>14</v>
@@ -30806,11 +30803,11 @@
         <v>13</v>
       </c>
       <c r="I1044" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1044" s="8"/>
       <c r="K1044" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1045" customHeight="1" spans="1:11">
@@ -30818,7 +30815,7 @@
         <v>20</v>
       </c>
       <c r="B1045" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C1045" s="4">
         <v>14</v>
@@ -30831,11 +30828,11 @@
       <c r="G1045" s="4"/>
       <c r="H1045" s="4"/>
       <c r="I1045" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1045" s="8"/>
       <c r="K1045" s="4" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1046" customHeight="1" spans="1:11">
@@ -30843,7 +30840,7 @@
         <v>11</v>
       </c>
       <c r="B1046" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C1046" s="4">
         <v>13</v>
@@ -30858,11 +30855,11 @@
         <v>13</v>
       </c>
       <c r="I1046" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1046" s="8"/>
       <c r="K1046" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1047" customHeight="1" spans="1:11">
@@ -30870,7 +30867,7 @@
         <v>18</v>
       </c>
       <c r="B1047" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C1047" s="4">
         <v>13</v>
@@ -30883,7 +30880,7 @@
       <c r="G1047" s="4"/>
       <c r="H1047" s="4"/>
       <c r="I1047" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1047" s="8">
         <v>1193.55</v>
@@ -30895,7 +30892,7 @@
         <v>24</v>
       </c>
       <c r="B1048" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C1048" s="4">
         <v>12</v>
@@ -30910,7 +30907,7 @@
         <v>23</v>
       </c>
       <c r="I1048" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1048" s="8">
         <v>600</v>
@@ -30922,7 +30919,7 @@
         <v>18</v>
       </c>
       <c r="B1049" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C1049" s="4">
         <v>12</v>
@@ -30934,10 +30931,10 @@
       <c r="F1049" s="4"/>
       <c r="G1049" s="4"/>
       <c r="H1049" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I1049" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1049" s="8">
         <v>71.18</v>
@@ -30949,7 +30946,7 @@
         <v>18</v>
       </c>
       <c r="B1050" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C1050" s="4">
         <v>12</v>
@@ -30964,7 +30961,7 @@
         <v>23</v>
       </c>
       <c r="I1050" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1050" s="8">
         <v>2800</v>
@@ -30976,7 +30973,7 @@
         <v>24</v>
       </c>
       <c r="B1051" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C1051" s="4">
         <v>11</v>
@@ -30991,7 +30988,7 @@
         <v>23</v>
       </c>
       <c r="I1051" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1051" s="8">
         <v>1825</v>
@@ -31003,7 +31000,7 @@
         <v>18</v>
       </c>
       <c r="B1052" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C1052" s="4">
         <v>11</v>
@@ -31018,7 +31015,7 @@
         <v>23</v>
       </c>
       <c r="I1052" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1052" s="8">
         <v>876</v>
@@ -31030,7 +31027,7 @@
         <v>18</v>
       </c>
       <c r="B1053" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C1053" s="4">
         <v>9</v>
@@ -31043,7 +31040,7 @@
       <c r="G1053" s="4"/>
       <c r="H1053" s="4"/>
       <c r="I1053" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1053" s="8">
         <v>341.28</v>
@@ -31055,7 +31052,7 @@
         <v>11</v>
       </c>
       <c r="B1054" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C1054" s="4">
         <v>7</v>
@@ -31070,11 +31067,11 @@
         <v>13</v>
       </c>
       <c r="I1054" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1054" s="8"/>
       <c r="K1054" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1055" customHeight="1" spans="1:11">
@@ -31082,7 +31079,7 @@
         <v>11</v>
       </c>
       <c r="B1055" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C1055" s="4">
         <v>6</v>
@@ -31095,11 +31092,11 @@
       <c r="G1055" s="4"/>
       <c r="H1055" s="4"/>
       <c r="I1055" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1055" s="8"/>
       <c r="K1055" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="1056" customHeight="1" spans="1:11">
@@ -31107,7 +31104,7 @@
         <v>11</v>
       </c>
       <c r="B1056" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C1056" s="4">
         <v>5</v>
@@ -31122,11 +31119,11 @@
         <v>13</v>
       </c>
       <c r="I1056" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1056" s="8"/>
       <c r="K1056" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="1057" customHeight="1" spans="1:11">
@@ -31134,7 +31131,7 @@
         <v>20</v>
       </c>
       <c r="B1057" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C1057" s="4">
         <v>5</v>
@@ -31149,13 +31146,13 @@
         <v>436</v>
       </c>
       <c r="I1057" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1057" s="8">
         <v>5212</v>
       </c>
       <c r="K1057" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1058" customHeight="1" spans="1:11">
@@ -31163,7 +31160,7 @@
         <v>11</v>
       </c>
       <c r="B1058" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C1058" s="4">
         <v>4</v>
@@ -31176,11 +31173,11 @@
       <c r="G1058" s="4"/>
       <c r="H1058" s="4"/>
       <c r="I1058" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1058" s="8"/>
       <c r="K1058" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="1059" customHeight="1" spans="1:11">
@@ -31188,7 +31185,7 @@
         <v>11</v>
       </c>
       <c r="B1059" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C1059" s="4">
         <v>4</v>
@@ -31201,7 +31198,7 @@
       <c r="G1059" s="4"/>
       <c r="H1059" s="4"/>
       <c r="I1059" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1059" s="8">
         <v>1400</v>
@@ -31213,7 +31210,7 @@
         <v>24</v>
       </c>
       <c r="B1060" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C1060" s="4">
         <v>4</v>
@@ -31226,7 +31223,7 @@
       <c r="G1060" s="4"/>
       <c r="H1060" s="4"/>
       <c r="I1060" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1060" s="8">
         <v>1398</v>
@@ -31238,7 +31235,7 @@
         <v>33</v>
       </c>
       <c r="B1061" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C1061" s="4">
         <v>4</v>
@@ -31253,7 +31250,7 @@
         <v>23</v>
       </c>
       <c r="I1061" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1061" s="8"/>
       <c r="K1061" s="4"/>
@@ -31263,7 +31260,7 @@
         <v>20</v>
       </c>
       <c r="B1062" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C1062" s="4">
         <v>3</v>
@@ -31278,11 +31275,11 @@
         <v>23</v>
       </c>
       <c r="I1062" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1062" s="8"/>
       <c r="K1062" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1063" customHeight="1" spans="1:11">
@@ -31290,7 +31287,7 @@
         <v>11</v>
       </c>
       <c r="B1063" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C1063" s="4">
         <v>1</v>
@@ -31303,11 +31300,11 @@
       <c r="G1063" s="4"/>
       <c r="H1063" s="4"/>
       <c r="I1063" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1063" s="8"/>
       <c r="K1063" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="1064" customHeight="1" spans="1:11">
@@ -31315,7 +31312,7 @@
         <v>20</v>
       </c>
       <c r="B1064" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C1064" s="4">
         <v>1</v>
@@ -31328,7 +31325,7 @@
       <c r="G1064" s="4"/>
       <c r="H1064" s="4"/>
       <c r="I1064" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1064" s="8">
         <v>482</v>
@@ -31340,7 +31337,7 @@
         <v>20</v>
       </c>
       <c r="B1065" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C1065" s="4">
         <v>293</v>
@@ -31355,13 +31352,13 @@
         <v>32</v>
       </c>
       <c r="I1065" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1065" s="8">
         <v>3060</v>
       </c>
       <c r="K1065" s="4" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1066" customHeight="1" spans="1:11">
@@ -31369,7 +31366,7 @@
         <v>20</v>
       </c>
       <c r="B1066" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C1066" s="4">
         <v>281</v>
@@ -31384,13 +31381,13 @@
         <v>13</v>
       </c>
       <c r="I1066" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1066" s="8">
         <v>2760</v>
       </c>
       <c r="K1066" s="4" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1067" customHeight="1" spans="1:11">
@@ -31398,7 +31395,7 @@
         <v>20</v>
       </c>
       <c r="B1067" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C1067" s="4">
         <v>241</v>
@@ -31413,13 +31410,13 @@
         <v>13</v>
       </c>
       <c r="I1067" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1067" s="8">
         <v>1800</v>
       </c>
       <c r="K1067" s="4" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1068" customHeight="1" spans="1:11">
@@ -31427,7 +31424,7 @@
         <v>20</v>
       </c>
       <c r="B1068" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C1068" s="4">
         <v>139</v>
@@ -31444,11 +31441,11 @@
         <v>462</v>
       </c>
       <c r="I1068" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1068" s="8"/>
       <c r="K1068" s="4" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1069" customHeight="1" spans="1:11">
@@ -31456,7 +31453,7 @@
         <v>20</v>
       </c>
       <c r="B1069" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C1069" s="4">
         <v>111</v>
@@ -31471,13 +31468,13 @@
         <v>13</v>
       </c>
       <c r="I1069" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1069" s="8">
         <v>1080</v>
       </c>
       <c r="K1069" s="4" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1070" customHeight="1" spans="1:11">
@@ -31485,7 +31482,7 @@
         <v>20</v>
       </c>
       <c r="B1070" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C1070" s="4">
         <v>108</v>
@@ -31500,13 +31497,13 @@
         <v>23</v>
       </c>
       <c r="I1070" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1070" s="8">
         <v>2470</v>
       </c>
       <c r="K1070" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1071" customHeight="1" spans="1:11">
@@ -31514,7 +31511,7 @@
         <v>20</v>
       </c>
       <c r="B1071" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C1071" s="4">
         <v>85</v>
@@ -31529,13 +31526,13 @@
         <v>23</v>
       </c>
       <c r="I1071" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1071" s="8">
         <v>660</v>
       </c>
       <c r="K1071" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1072" customHeight="1" spans="1:11">
@@ -31543,7 +31540,7 @@
         <v>20</v>
       </c>
       <c r="B1072" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C1072" s="4">
         <v>76</v>
@@ -31558,13 +31555,13 @@
         <v>32</v>
       </c>
       <c r="I1072" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1072" s="8">
         <v>1440</v>
       </c>
       <c r="K1072" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1073" customHeight="1" spans="1:11">
@@ -31572,7 +31569,7 @@
         <v>33</v>
       </c>
       <c r="B1073" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C1073" s="4">
         <v>75</v>
@@ -31587,11 +31584,11 @@
         <v>436</v>
       </c>
       <c r="I1073" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1073" s="8"/>
       <c r="K1073" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1074" customHeight="1" spans="1:11">
@@ -31599,7 +31596,7 @@
         <v>20</v>
       </c>
       <c r="B1074" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C1074" s="4">
         <v>59</v>
@@ -31614,13 +31611,13 @@
         <v>23</v>
       </c>
       <c r="I1074" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1074" s="8">
         <v>960</v>
       </c>
       <c r="K1074" s="4" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1075" customHeight="1" spans="1:11">
@@ -31628,7 +31625,7 @@
         <v>20</v>
       </c>
       <c r="B1075" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C1075" s="4">
         <v>53</v>
@@ -31645,13 +31642,13 @@
         <v>462</v>
       </c>
       <c r="I1075" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1075" s="8">
         <v>1920</v>
       </c>
       <c r="K1075" s="4" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1076" customHeight="1" spans="1:11">
@@ -31659,7 +31656,7 @@
         <v>33</v>
       </c>
       <c r="B1076" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C1076" s="4">
         <v>51</v>
@@ -31674,13 +31671,13 @@
         <v>436</v>
       </c>
       <c r="I1076" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1076" s="8">
         <v>960</v>
       </c>
       <c r="K1076" s="4" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1077" customHeight="1" spans="1:11">
@@ -31688,7 +31685,7 @@
         <v>20</v>
       </c>
       <c r="B1077" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C1077" s="4">
         <v>46</v>
@@ -31703,13 +31700,13 @@
         <v>23</v>
       </c>
       <c r="I1077" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1077" s="8">
         <v>1200</v>
       </c>
       <c r="K1077" s="4" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1078" customHeight="1" spans="1:11">
@@ -31717,7 +31714,7 @@
         <v>20</v>
       </c>
       <c r="B1078" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1078" s="4">
         <v>46</v>
@@ -31732,11 +31729,11 @@
         <v>23</v>
       </c>
       <c r="I1078" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1078" s="8"/>
       <c r="K1078" s="4" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1079" customHeight="1" spans="1:11">
@@ -31744,7 +31741,7 @@
         <v>20</v>
       </c>
       <c r="B1079" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C1079" s="4">
         <v>38</v>
@@ -31759,13 +31756,13 @@
         <v>13</v>
       </c>
       <c r="I1079" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1079" s="8">
         <v>1020</v>
       </c>
       <c r="K1079" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1080" customHeight="1" spans="1:11">
@@ -31773,7 +31770,7 @@
         <v>20</v>
       </c>
       <c r="B1080" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C1080" s="4">
         <v>38</v>
@@ -31788,13 +31785,13 @@
         <v>23</v>
       </c>
       <c r="I1080" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1080" s="8">
         <v>720</v>
       </c>
       <c r="K1080" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1081" customHeight="1" spans="1:11">
@@ -31802,7 +31799,7 @@
         <v>20</v>
       </c>
       <c r="B1081" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C1081" s="4">
         <v>24</v>
@@ -31817,7 +31814,7 @@
         <v>23</v>
       </c>
       <c r="I1081" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1081" s="8">
         <v>960</v>
@@ -31829,7 +31826,7 @@
         <v>33</v>
       </c>
       <c r="B1082" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C1082" s="4">
         <v>22</v>
@@ -31844,13 +31841,13 @@
         <v>13</v>
       </c>
       <c r="I1082" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1082" s="8">
         <v>840</v>
       </c>
       <c r="K1082" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1083" customHeight="1" spans="1:11">
@@ -31858,7 +31855,7 @@
         <v>20</v>
       </c>
       <c r="B1083" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C1083" s="4">
         <v>22</v>
@@ -31873,11 +31870,11 @@
         <v>13</v>
       </c>
       <c r="I1083" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1083" s="8"/>
       <c r="K1083" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1084" customHeight="1" spans="1:11">
@@ -31885,7 +31882,7 @@
         <v>20</v>
       </c>
       <c r="B1084" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C1084" s="4">
         <v>21</v>
@@ -31900,11 +31897,11 @@
         <v>23</v>
       </c>
       <c r="I1084" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1084" s="8"/>
       <c r="K1084" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1085" customHeight="1" spans="1:11">
@@ -31912,7 +31909,7 @@
         <v>33</v>
       </c>
       <c r="B1085" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C1085" s="4">
         <v>17</v>
@@ -31927,11 +31924,11 @@
         <v>23</v>
       </c>
       <c r="I1085" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1085" s="8"/>
       <c r="K1085" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1086" customHeight="1" spans="1:11">
@@ -31939,7 +31936,7 @@
         <v>20</v>
       </c>
       <c r="B1086" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C1086" s="4">
         <v>15</v>
@@ -31952,13 +31949,13 @@
       <c r="G1086" s="4"/>
       <c r="H1086" s="4"/>
       <c r="I1086" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1086" s="8">
         <v>480</v>
       </c>
       <c r="K1086" s="4" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1087" customHeight="1" spans="1:11">
@@ -31966,7 +31963,7 @@
         <v>33</v>
       </c>
       <c r="B1087" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C1087" s="4">
         <v>14</v>
@@ -31981,11 +31978,11 @@
         <v>795</v>
       </c>
       <c r="I1087" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1087" s="8"/>
       <c r="K1087" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1088" customHeight="1" spans="1:11">
@@ -31993,7 +31990,7 @@
         <v>20</v>
       </c>
       <c r="B1088" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C1088" s="4">
         <v>11</v>
@@ -32008,11 +32005,11 @@
         <v>23</v>
       </c>
       <c r="I1088" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1088" s="8"/>
       <c r="K1088" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1089" customHeight="1" spans="1:11">
@@ -32020,7 +32017,7 @@
         <v>18</v>
       </c>
       <c r="B1089" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C1089" s="4">
         <v>10</v>
@@ -32035,13 +32032,13 @@
         <v>23</v>
       </c>
       <c r="I1089" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1089" s="8">
         <v>60</v>
       </c>
       <c r="K1089" s="4" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1090" customHeight="1" spans="1:11">
@@ -32049,7 +32046,7 @@
         <v>20</v>
       </c>
       <c r="B1090" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C1090" s="4">
         <v>10</v>
@@ -32064,13 +32061,13 @@
         <v>23</v>
       </c>
       <c r="I1090" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1090" s="8">
         <v>600</v>
       </c>
       <c r="K1090" s="4" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="1091" customHeight="1" spans="1:11">
@@ -32078,7 +32075,7 @@
         <v>33</v>
       </c>
       <c r="B1091" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C1091" s="4">
         <v>9</v>
@@ -32095,11 +32092,11 @@
         <v>785</v>
       </c>
       <c r="I1091" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1091" s="8"/>
       <c r="K1091" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1092" customHeight="1" spans="1:11">
@@ -32107,7 +32104,7 @@
         <v>20</v>
       </c>
       <c r="B1092" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C1092" s="4">
         <v>8</v>
@@ -32122,13 +32119,13 @@
         <v>23</v>
       </c>
       <c r="I1092" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1092" s="8">
         <v>240</v>
       </c>
       <c r="K1092" s="4" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1093" customHeight="1" spans="1:11">
@@ -32136,7 +32133,7 @@
         <v>33</v>
       </c>
       <c r="B1093" s="3" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C1093" s="4">
         <v>6</v>
@@ -32151,13 +32148,13 @@
         <v>23</v>
       </c>
       <c r="I1093" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1093" s="8">
         <v>960</v>
       </c>
       <c r="K1093" s="4" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="1094" customHeight="1" spans="1:11">
@@ -32165,7 +32162,7 @@
         <v>20</v>
       </c>
       <c r="B1094" s="3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C1094" s="4">
         <v>5</v>
@@ -32178,13 +32175,13 @@
       <c r="G1094" s="4"/>
       <c r="H1094" s="4"/>
       <c r="I1094" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1094" s="8">
         <v>960</v>
       </c>
       <c r="K1094" s="4" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1095" customHeight="1" spans="1:11">
@@ -32192,7 +32189,7 @@
         <v>20</v>
       </c>
       <c r="B1095" s="3" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C1095" s="4">
         <v>2</v>
@@ -32207,13 +32204,13 @@
         <v>23</v>
       </c>
       <c r="I1095" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1095" s="8">
         <v>600</v>
       </c>
       <c r="K1095" s="4" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1096" customHeight="1" spans="1:11">
@@ -32221,7 +32218,7 @@
         <v>20</v>
       </c>
       <c r="B1096" s="3" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C1096" s="4">
         <v>2</v>
@@ -32236,13 +32233,13 @@
         <v>23</v>
       </c>
       <c r="I1096" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1096" s="8">
         <v>1920</v>
       </c>
       <c r="K1096" s="4" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="1097" customHeight="1" spans="1:11">
@@ -32250,7 +32247,7 @@
         <v>24</v>
       </c>
       <c r="B1097" s="3" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C1097" s="4">
         <v>1</v>
@@ -32265,13 +32262,13 @@
         <v>32</v>
       </c>
       <c r="I1097" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1097" s="8">
         <v>1440</v>
       </c>
       <c r="K1097" s="4" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="1098" customHeight="1" spans="1:11">
@@ -32279,7 +32276,7 @@
         <v>20</v>
       </c>
       <c r="B1098" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C1098" s="4">
         <v>1</v>
@@ -32292,11 +32289,11 @@
       <c r="G1098" s="4"/>
       <c r="H1098" s="4"/>
       <c r="I1098" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1098" s="8"/>
       <c r="K1098" s="4" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1099" customHeight="1" spans="1:11">
@@ -32304,7 +32301,7 @@
         <v>20</v>
       </c>
       <c r="B1099" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C1099" s="4">
         <v>1</v>
@@ -32317,13 +32314,13 @@
       <c r="G1099" s="4"/>
       <c r="H1099" s="4"/>
       <c r="I1099" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1099" s="8">
         <v>360</v>
       </c>
       <c r="K1099" s="4" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1100" customHeight="1" spans="1:11">
@@ -32331,7 +32328,7 @@
         <v>20</v>
       </c>
       <c r="B1100" s="3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C1100" s="4">
         <v>1</v>
@@ -32344,11 +32341,11 @@
       <c r="G1100" s="4"/>
       <c r="H1100" s="4"/>
       <c r="I1100" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J1100" s="8"/>
       <c r="K1100" s="4" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
   </sheetData>
